--- a/sports_forms/002_flag_football_league_registration_form--sports_forms.xlsx
+++ b/sports_forms/002_flag_football_league_registration_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1925,17 +1925,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>team_manager_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>player_manager</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>Player Manager</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>player_manager</t>
+          <t>team_manager</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Player Manager</t>
+          <t>Team Manager</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>team_manager</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Team Manager</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>team_manager_choices</t>
+          <t>team_manager_state_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>al</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ak</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>az</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ct</t>
+          <t>dc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>fl</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ga</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>il</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ia</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ky</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>la</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>mn</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>mt</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nv</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ut</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -2661,46 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>wv</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WV</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>team_manager_state_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>wi</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
           <t>WI</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>team_manager_state_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>CO</t>
         </is>
       </c>
     </row>
